--- a/main/ig/StructureDefinition-fr-cda-points-de-vigilances-non-code.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-points-de-vigilances-non-code.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T15:11:12+00:00</t>
+    <t>2026-04-23T15:25:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-points-de-vigilances-non-code.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-points-de-vigilances-non-code.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T15:25:59+00:00</t>
+    <t>2026-05-06T07:44:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-points-de-vigilances-non-code.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-points-de-vigilances-non-code.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T07:44:21+00:00</t>
+    <t>2026-05-13T14:53:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-points-de-vigilances-non-code.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-points-de-vigilances-non-code.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:53:03+00:00</t>
+    <t>2026-05-15T08:08:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-points-de-vigilances-non-code.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-points-de-vigilances-non-code.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:35:10+00:00</t>
+    <t>2026-06-29T12:53:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-points-de-vigilances-non-code.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-points-de-vigilances-non-code.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1728" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1742" uniqueCount="249">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:53:00+00:00</t>
+    <t>2026-06-29T14:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -454,6 +454,9 @@
 </t>
   </si>
   <si>
+    <t>Can serve as a target of a linkHtml reference</t>
+  </si>
+  <si>
     <t>Section.classCode</t>
   </si>
   <si>
@@ -643,6 +646,9 @@
     <t>Titre de la section</t>
   </si>
   <si>
+    <t>If valued, it is to be rendered as part of the narrative content of the clinical document body.</t>
+  </si>
+  <si>
     <t>Section.text</t>
   </si>
   <si>
@@ -653,10 +659,25 @@
     <t>Bloc narratif</t>
   </si>
   <si>
+    <t>Also referred to as the CDA Narrative Block</t>
+  </si>
+  <si>
     <t>Section.confidentialityCode</t>
   </si>
   <si>
+    <t>Controls the disclosure of information in this section</t>
+  </si>
+  <si>
+    <t>A value for Section.confidentialityCode overrides the value propagated from StructuredBody.</t>
+  </si>
+  <si>
     <t>Section.languageCode</t>
+  </si>
+  <si>
+    <t>Human language of character data</t>
+  </si>
+  <si>
+    <t>A value for Section.languageCode overrides the value propagated from StructuredBody.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/all-languages</t>
@@ -669,6 +690,15 @@
 </t>
   </si>
   <si>
+    <t>Primary target of the entries recorded in a section</t>
+  </si>
+  <si>
+    <t>Most of the time the subject is the same as the recordTarget, but need not be, for instance when the subject is a fetus observed in an obstetrical ultrasound.</t>
+  </si>
+  <si>
+    <t>The subject participant can be ascribed to a CDA section or a CDA entry. It propagates to nested components, unless overridden. The subject of a document is presumed to be the patient.</t>
+  </si>
+  <si>
     <t>Section.author</t>
   </si>
   <si>
@@ -676,6 +706,9 @@
 </t>
   </si>
   <si>
+    <t>The author participant can be ascribed to a CDA section, where it overrides the value(s) propagated from the CDA header.</t>
+  </si>
+  <si>
     <t>Section.informant</t>
   </si>
   <si>
@@ -683,6 +716,9 @@
 </t>
   </si>
   <si>
+    <t>The informant participant can be ascribed to a CDA section where it overrides the value(s) propagated from the CDA header.</t>
+  </si>
+  <si>
     <t>Section.entry</t>
   </si>
   <si>
@@ -695,6 +731,12 @@
   <si>
     <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/InfrastructureRoot
 </t>
+  </si>
+  <si>
+    <t>Used to nest a Section within a Section</t>
+  </si>
+  <si>
+    <t>Context propagates to nested sections</t>
   </si>
   <si>
     <t>Section.component.nullFlavor</t>
@@ -1077,7 +1119,7 @@
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="13.4296875" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="148.87109375" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
@@ -2880,7 +2922,9 @@
       <c r="K18" t="s" s="2">
         <v>141</v>
       </c>
-      <c r="L18" s="2"/>
+      <c r="L18" t="s" s="2">
+        <v>142</v>
+      </c>
       <c r="M18" s="2"/>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2951,10 +2995,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2988,7 +3032,7 @@
       </c>
       <c r="Q19" s="2"/>
       <c r="R19" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="S19" t="s" s="2">
         <v>74</v>
@@ -3010,7 +3054,7 @@
       </c>
       <c r="Y19" s="2"/>
       <c r="Z19" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>74</v>
@@ -3028,7 +3072,7 @@
         <v>74</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -3048,10 +3092,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3085,7 +3129,7 @@
       </c>
       <c r="Q20" s="2"/>
       <c r="R20" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="S20" t="s" s="2">
         <v>74</v>
@@ -3107,7 +3151,7 @@
       </c>
       <c r="Y20" s="2"/>
       <c r="Z20" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>74</v>
@@ -3125,7 +3169,7 @@
         <v>74</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -3145,10 +3189,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3162,7 +3206,7 @@
         <v>75</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>74</v>
@@ -3174,10 +3218,10 @@
         <v>95</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3228,7 +3272,7 @@
         <v>74</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -3248,10 +3292,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3265,7 +3309,7 @@
         <v>75</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>74</v>
@@ -3274,13 +3318,13 @@
         <v>74</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3331,7 +3375,7 @@
         <v>74</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -3351,10 +3395,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3452,10 +3496,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3471,7 +3515,7 @@
         <v>75</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>74</v>
@@ -3484,7 +3528,7 @@
       </c>
       <c r="L24" s="2"/>
       <c r="M24" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3496,7 +3540,7 @@
         <v>74</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>74</v>
@@ -3535,7 +3579,7 @@
         <v>74</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -3555,17 +3599,17 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E25" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F25" t="s" s="2">
         <v>75</v>
@@ -3574,7 +3618,7 @@
         <v>75</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>74</v>
@@ -3587,7 +3631,7 @@
       </c>
       <c r="L25" s="2"/>
       <c r="M25" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3599,7 +3643,7 @@
         <v>74</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="T25" t="s" s="2">
         <v>74</v>
@@ -3638,7 +3682,7 @@
         <v>74</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -3658,17 +3702,17 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E26" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F26" t="s" s="2">
         <v>80</v>
@@ -3690,7 +3734,7 @@
       </c>
       <c r="L26" s="2"/>
       <c r="M26" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3702,7 +3746,7 @@
         <v>74</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="T26" t="s" s="2">
         <v>74</v>
@@ -3741,7 +3785,7 @@
         <v>74</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -3761,17 +3805,17 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E27" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F27" t="s" s="2">
         <v>80</v>
@@ -3793,7 +3837,7 @@
       </c>
       <c r="L27" s="2"/>
       <c r="M27" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3844,7 +3888,7 @@
         <v>74</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -3864,17 +3908,17 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E28" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F28" t="s" s="2">
         <v>75</v>
@@ -3883,7 +3927,7 @@
         <v>75</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>74</v>
@@ -3896,7 +3940,7 @@
       </c>
       <c r="L28" s="2"/>
       <c r="M28" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3908,7 +3952,7 @@
         <v>74</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="T28" t="s" s="2">
         <v>74</v>
@@ -3947,7 +3991,7 @@
         <v>74</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -3967,10 +4011,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3993,11 +4037,11 @@
         <v>74</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="L29" s="2"/>
       <c r="M29" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4048,7 +4092,7 @@
         <v>74</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -4068,10 +4112,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4098,7 +4142,7 @@
       </c>
       <c r="L30" s="2"/>
       <c r="M30" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4149,7 +4193,7 @@
         <v>74</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -4169,17 +4213,17 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E31" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F31" t="s" s="2">
         <v>80</v>
@@ -4197,11 +4241,11 @@
         <v>74</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L31" s="2"/>
       <c r="M31" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4252,7 +4296,7 @@
         <v>74</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -4272,17 +4316,17 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E32" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F32" t="s" s="2">
         <v>80</v>
@@ -4300,11 +4344,11 @@
         <v>74</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L32" s="2"/>
       <c r="M32" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4355,7 +4399,7 @@
         <v>74</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -4375,17 +4419,17 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E33" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F33" t="s" s="2">
         <v>80</v>
@@ -4403,11 +4447,11 @@
         <v>74</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L33" s="2"/>
       <c r="M33" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4458,7 +4502,7 @@
         <v>74</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -4478,10 +4522,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4495,7 +4539,7 @@
         <v>75</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>74</v>
@@ -4504,16 +4548,18 @@
         <v>74</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="N34" s="2"/>
-      <c r="O34" s="2"/>
+      <c r="O34" t="s" s="2">
+        <v>204</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>74</v>
       </c>
@@ -4561,7 +4607,7 @@
         <v>74</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -4581,10 +4627,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4598,7 +4644,7 @@
         <v>75</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>74</v>
@@ -4607,15 +4653,17 @@
         <v>74</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="N35" s="2"/>
+        <v>207</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>208</v>
+      </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>74</v>
@@ -4664,7 +4712,7 @@
         <v>74</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -4684,10 +4732,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4710,12 +4758,16 @@
         <v>74</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="L36" s="2"/>
+        <v>153</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>210</v>
+      </c>
       <c r="M36" s="2"/>
       <c r="N36" s="2"/>
-      <c r="O36" s="2"/>
+      <c r="O36" t="s" s="2">
+        <v>211</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>74</v>
       </c>
@@ -4763,7 +4815,7 @@
         <v>74</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -4783,10 +4835,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -4811,10 +4863,14 @@
       <c r="K37" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="L37" s="2"/>
+      <c r="L37" t="s" s="2">
+        <v>213</v>
+      </c>
       <c r="M37" s="2"/>
       <c r="N37" s="2"/>
-      <c r="O37" s="2"/>
+      <c r="O37" t="s" s="2">
+        <v>214</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>74</v>
       </c>
@@ -4842,7 +4898,7 @@
       </c>
       <c r="Y37" s="2"/>
       <c r="Z37" t="s" s="2">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>74</v>
@@ -4860,7 +4916,7 @@
         <v>74</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -4880,10 +4936,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -4906,12 +4962,18 @@
         <v>74</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="L38" s="2"/>
+        <v>217</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>218</v>
+      </c>
       <c r="M38" s="2"/>
-      <c r="N38" s="2"/>
-      <c r="O38" s="2"/>
+      <c r="N38" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>220</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>74</v>
       </c>
@@ -4959,7 +5021,7 @@
         <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -4979,10 +5041,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5005,12 +5067,14 @@
         <v>74</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="L39" s="2"/>
       <c r="M39" s="2"/>
       <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
+      <c r="O39" t="s" s="2">
+        <v>223</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>74</v>
       </c>
@@ -5058,7 +5122,7 @@
         <v>74</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -5078,10 +5142,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5104,12 +5168,14 @@
         <v>74</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="L40" s="2"/>
       <c r="M40" s="2"/>
       <c r="N40" s="2"/>
-      <c r="O40" s="2"/>
+      <c r="O40" t="s" s="2">
+        <v>226</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>74</v>
       </c>
@@ -5157,7 +5223,7 @@
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -5177,10 +5243,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5203,7 +5269,7 @@
         <v>74</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="L41" s="2"/>
       <c r="M41" s="2"/>
@@ -5256,7 +5322,7 @@
         <v>74</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -5276,10 +5342,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5302,12 +5368,16 @@
         <v>74</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="L42" s="2"/>
+        <v>230</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>231</v>
+      </c>
       <c r="M42" s="2"/>
       <c r="N42" s="2"/>
-      <c r="O42" s="2"/>
+      <c r="O42" t="s" s="2">
+        <v>232</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>74</v>
       </c>
@@ -5355,7 +5425,7 @@
         <v>74</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -5375,10 +5445,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5476,10 +5546,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -5577,10 +5647,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -5678,10 +5748,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -5779,10 +5849,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -5882,10 +5952,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -5985,10 +6055,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6088,10 +6158,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6191,10 +6261,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6292,10 +6362,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6322,7 +6392,7 @@
       </c>
       <c r="L52" s="2"/>
       <c r="M52" t="s" s="2">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -6331,7 +6401,7 @@
       </c>
       <c r="Q52" s="2"/>
       <c r="R52" t="s" s="2">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="S52" t="s" s="2">
         <v>74</v>
@@ -6373,7 +6443,7 @@
         <v>74</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -6393,10 +6463,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6430,7 +6500,7 @@
       </c>
       <c r="Q53" s="2"/>
       <c r="R53" t="s" s="2">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="S53" t="s" s="2">
         <v>74</v>
@@ -6472,7 +6542,7 @@
         <v>74</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -6492,10 +6562,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -6518,7 +6588,7 @@
         <v>74</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="L54" s="2"/>
       <c r="M54" s="2"/>
@@ -6571,7 +6641,7 @@
         <v>74</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>75</v>

--- a/main/ig/StructureDefinition-fr-cda-points-de-vigilances-non-code.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-points-de-vigilances-non-code.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T14:20:03+00:00</t>
+    <t>2026-06-29T15:28:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-points-de-vigilances-non-code.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-points-de-vigilances-non-code.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T15:28:29+00:00</t>
+    <t>2026-06-30T08:01:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-points-de-vigilances-non-code.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-points-de-vigilances-non-code.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T08:01:58+00:00</t>
+    <t>2026-06-30T09:01:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-points-de-vigilances-non-code.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-points-de-vigilances-non-code.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:01:37+00:00</t>
+    <t>2026-06-30T09:56:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-points-de-vigilances-non-code.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-points-de-vigilances-non-code.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:56:22+00:00</t>
+    <t>2026-08-06T11:33:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
